--- a/artfynd/A 61054-2025 artfynd.xlsx
+++ b/artfynd/A 61054-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135592917</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135592923</v>
       </c>
       <c r="B3" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135592918</v>
       </c>
       <c r="B4" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135592921</v>
       </c>
       <c r="B5" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135592929</v>
       </c>
       <c r="B6" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135592920</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135592955</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135592928</v>
       </c>
       <c r="B9" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135592954</v>
       </c>
       <c r="B10" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135592925</v>
       </c>
       <c r="B11" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135592932</v>
       </c>
       <c r="B12" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135592914</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>135592915</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>135592916</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>135592958</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>135592922</v>
       </c>
       <c r="B17" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135592924</v>
       </c>
       <c r="B18" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135592927</v>
       </c>
       <c r="B19" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>135592930</v>
       </c>
       <c r="B20" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>135592931</v>
       </c>
       <c r="B21" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>135592926</v>
       </c>
       <c r="B22" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>135592943</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>135592947</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135592953</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>135592934</v>
       </c>
       <c r="B26" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135592941</v>
       </c>
       <c r="B27" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135592950</v>
       </c>
       <c r="B28" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>135592952</v>
       </c>
       <c r="B29" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>135592945</v>
       </c>
       <c r="B30" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>135592942</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>135592948</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>135592933</v>
       </c>
       <c r="B33" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>135592940</v>
       </c>
       <c r="B34" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>135592951</v>
       </c>
       <c r="B35" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 61054-2025 artfynd.xlsx
+++ b/artfynd/A 61054-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135592917</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135592923</v>
       </c>
       <c r="B3" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135592918</v>
       </c>
       <c r="B4" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135592921</v>
       </c>
       <c r="B5" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135592929</v>
       </c>
       <c r="B6" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135592920</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135592955</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135592928</v>
       </c>
       <c r="B9" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135592954</v>
       </c>
       <c r="B10" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135592925</v>
       </c>
       <c r="B11" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135592932</v>
       </c>
       <c r="B12" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>135592922</v>
       </c>
       <c r="B17" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135592924</v>
       </c>
       <c r="B18" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135592927</v>
       </c>
       <c r="B19" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>135592930</v>
       </c>
       <c r="B20" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>135592931</v>
       </c>
       <c r="B21" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>135592926</v>
       </c>
       <c r="B22" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>135592943</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>135592947</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135592953</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>135592934</v>
       </c>
       <c r="B26" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135592941</v>
       </c>
       <c r="B27" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135592950</v>
       </c>
       <c r="B28" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>135592952</v>
       </c>
       <c r="B29" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>135592945</v>
       </c>
       <c r="B30" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>135592933</v>
       </c>
       <c r="B33" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>135592940</v>
       </c>
       <c r="B34" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>135592951</v>
       </c>
       <c r="B35" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 61054-2025 artfynd.xlsx
+++ b/artfynd/A 61054-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135592917</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135592923</v>
       </c>
       <c r="B3" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135592918</v>
       </c>
       <c r="B4" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135592921</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135592929</v>
       </c>
       <c r="B6" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61054-2025 artfynd.xlsx
+++ b/artfynd/A 61054-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135592917</v>
       </c>
       <c r="B2" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135592923</v>
       </c>
       <c r="B3" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135592918</v>
       </c>
       <c r="B4" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135592921</v>
       </c>
       <c r="B5" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135592929</v>
       </c>
       <c r="B6" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135592920</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135592955</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135592928</v>
       </c>
       <c r="B9" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135592954</v>
       </c>
       <c r="B10" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135592925</v>
       </c>
       <c r="B11" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135592932</v>
       </c>
       <c r="B12" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135592914</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>135592915</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>135592916</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>135592958</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>135592922</v>
       </c>
       <c r="B17" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135592924</v>
       </c>
       <c r="B18" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135592927</v>
       </c>
       <c r="B19" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>135592930</v>
       </c>
       <c r="B20" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>135592931</v>
       </c>
       <c r="B21" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>135592926</v>
       </c>
       <c r="B22" t="n">
-        <v>80335</v>
+        <v>80337</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>135592943</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>135592947</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135592953</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>135592934</v>
       </c>
       <c r="B26" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135592941</v>
       </c>
       <c r="B27" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135592950</v>
       </c>
       <c r="B28" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>135592952</v>
       </c>
       <c r="B29" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>135592945</v>
       </c>
       <c r="B30" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>135592942</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>135592948</v>
       </c>
       <c r="B32" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>135592933</v>
       </c>
       <c r="B33" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>135592940</v>
       </c>
       <c r="B34" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>135592951</v>
       </c>
       <c r="B35" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 61054-2025 artfynd.xlsx
+++ b/artfynd/A 61054-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135592917</v>
       </c>
       <c r="B2" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135592923</v>
       </c>
       <c r="B3" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135592918</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135592921</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135592929</v>
       </c>
       <c r="B6" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135592920</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135592955</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135592928</v>
       </c>
       <c r="B9" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135592954</v>
       </c>
       <c r="B10" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135592925</v>
       </c>
       <c r="B11" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135592932</v>
       </c>
       <c r="B12" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>135592922</v>
       </c>
       <c r="B17" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135592924</v>
       </c>
       <c r="B18" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135592927</v>
       </c>
       <c r="B19" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>135592930</v>
       </c>
       <c r="B20" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>135592931</v>
       </c>
       <c r="B21" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>135592926</v>
       </c>
       <c r="B22" t="n">
-        <v>80337</v>
+        <v>80338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>135592943</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>135592947</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135592953</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>135592934</v>
       </c>
       <c r="B26" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135592941</v>
       </c>
       <c r="B27" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135592950</v>
       </c>
       <c r="B28" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>135592952</v>
       </c>
       <c r="B29" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>135592945</v>
       </c>
       <c r="B30" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>135592933</v>
       </c>
       <c r="B33" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>135592940</v>
       </c>
       <c r="B34" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>135592951</v>
       </c>
       <c r="B35" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 61054-2025 artfynd.xlsx
+++ b/artfynd/A 61054-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135592917</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135592923</v>
       </c>
       <c r="B3" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135592918</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135592921</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135592929</v>
       </c>
       <c r="B6" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
